--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,14</t>
+          <t>-1,69; 1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,26</t>
+          <t>-0,59; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,87</t>
+          <t>-1,56; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,16</t>
+          <t>-2,32; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,69</t>
+          <t>-0,31; 4,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,65</t>
+          <t>-1,87; 3,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,76</t>
+          <t>-1,53; 0,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 3,03</t>
+          <t>0,08; 2,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,49</t>
+          <t>-1,36; 2,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,2; 188,01</t>
+          <t>-82,7; 172,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 477,81</t>
+          <t>-35,93; 420,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 841,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,7; 113,63</t>
+          <t>-77,52; 95,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 354,57</t>
+          <t>-19,76; 371,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,1; 272,76</t>
+          <t>-74,55; 297,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,64; 64,43</t>
+          <t>-64,45; 68,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 229,5</t>
+          <t>-3,97; 217,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 177,92</t>
+          <t>-67,96; 194,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,5</t>
+          <t>-2,07; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,08</t>
+          <t>-1,3; 1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,18</t>
+          <t>-1,5; 2,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,91</t>
+          <t>-1,11; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,34</t>
+          <t>-0,56; 3,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,92</t>
+          <t>-1,3; 2,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,15</t>
+          <t>-1,14; 1,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,89</t>
+          <t>-0,52; 1,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,46</t>
+          <t>-0,86; 2,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,92; 44,77</t>
+          <t>-72,05; 44,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 153,58</t>
+          <t>-48,19; 136,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 249,06</t>
+          <t>-63,7; 188,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 209,78</t>
+          <t>-37,91; 200,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 248,68</t>
+          <t>-25,0; 234,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 202,82</t>
+          <t>-46,48; 206,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 79,34</t>
+          <t>-43,13; 61,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 120,69</t>
+          <t>-23,32; 126,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 147,96</t>
+          <t>-36,22; 137,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,48</t>
+          <t>-0,96; 3,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,4</t>
+          <t>-1,68; 2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,49</t>
+          <t>-2,38; 2,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,52</t>
+          <t>-2,6; 2,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,77</t>
+          <t>0,52; 5,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,2</t>
+          <t>-4,4; 0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,24</t>
+          <t>-0,93; 2,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,45</t>
+          <t>0,22; 3,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,43</t>
+          <t>-2,59; 0,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 155,59</t>
+          <t>-23,86; 149,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 101,87</t>
+          <t>-38,16; 114,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 104,43</t>
+          <t>-52,5; 115,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 71,59</t>
+          <t>-42,89; 74,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,57; 162,72</t>
+          <t>6,02; 166,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 5,28</t>
+          <t>-70,1; 2,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,46; 68,03</t>
+          <t>-19,31; 75,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 104,19</t>
+          <t>4,11; 112,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 13,93</t>
+          <t>-53,0; 12,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,1</t>
+          <t>-1,11; 2,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,09</t>
+          <t>0,81; 5,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,32</t>
+          <t>-1,75; 3,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,49</t>
+          <t>-2,77; 2,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,56; 10,17</t>
+          <t>3,55; 10,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,63</t>
+          <t>-3,09; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,94</t>
+          <t>-1,6; 1,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,89</t>
+          <t>2,9; 7,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,84</t>
+          <t>-1,91; 1,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 232,39</t>
+          <t>-40,18; 226,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,6; 402,89</t>
+          <t>12,94; 391,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 199,23</t>
+          <t>-50,12; 229,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 60,38</t>
+          <t>-40,95; 56,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,14; 245,63</t>
+          <t>48,63; 251,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 41,16</t>
+          <t>-41,9; 43,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 64,47</t>
+          <t>-33,42; 62,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,33; 230,55</t>
+          <t>57,02; 226,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 58,21</t>
+          <t>-39,76; 58,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,59</t>
+          <t>-3,64; 1,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,98</t>
+          <t>-0,04; 6,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,35</t>
+          <t>-2,95; 2,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,86</t>
+          <t>-2,92; 3,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,21; 17,67</t>
+          <t>8,85; 17,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,26</t>
+          <t>-2,25; 3,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,64</t>
+          <t>-2,26; 1,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,75; 11,19</t>
+          <t>5,61; 10,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,15</t>
+          <t>-1,74; 2,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 62,35</t>
+          <t>-61,93; 72,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 212,41</t>
+          <t>-5,5; 237,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 89,39</t>
+          <t>-51,2; 85,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 66,71</t>
+          <t>-41,96; 84,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>113,56; 425,69</t>
+          <t>114,98; 418,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 83,29</t>
+          <t>-29,23; 85,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 45,0</t>
+          <t>-38,36; 50,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>94,29; 292,4</t>
+          <t>91,09; 279,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 59,71</t>
+          <t>-27,71; 57,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,35</t>
+          <t>-2,9; 3,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,01</t>
+          <t>-3,22; 2,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,55</t>
+          <t>-3,91; 1,8</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,49</t>
+          <t>-1,61; 6,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,93</t>
+          <t>4,99; 14,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 68,14</t>
+          <t>-1,69; 65,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,8</t>
+          <t>-1,43; 3,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,76</t>
+          <t>2,04; 7,88</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 52,03</t>
+          <t>-1,6; 53,75</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 121,17</t>
+          <t>-53,9; 127,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 109,73</t>
+          <t>-54,85; 99,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-61,3; 67,21</t>
+          <t>-60,86; 81,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 125,7</t>
+          <t>-16,84; 126,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>52,11; 280,12</t>
+          <t>51,82; 270,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 1456,11</t>
+          <t>-22,25; 1565,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 80,08</t>
+          <t>-20,78; 82,04</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>26,86; 167,4</t>
+          <t>28,61; 175,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 1232,93</t>
+          <t>-26,0; 1249,62</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,63</t>
+          <t>-2,21; 5,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,08</t>
+          <t>1,12; 9,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,83</t>
+          <t>-1,66; 4,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,18</t>
+          <t>-4,72; 3,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,09; 15,14</t>
+          <t>5,08; 15,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,72</t>
+          <t>-4,83; 1,95</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,99</t>
+          <t>-2,64; 3,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,77</t>
+          <t>4,65; 11,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,04</t>
+          <t>-2,69; 2,05</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 314,76</t>
+          <t>-44,93; 298,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17,12; 492,52</t>
+          <t>10,11; 484,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 295,07</t>
+          <t>-34,18; 251,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 69,24</t>
+          <t>-50,03; 60,09</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>54,03; 320,43</t>
+          <t>51,45; 313,02</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 41,67</t>
+          <t>-50,56; 43,91</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 71,89</t>
+          <t>-37,03; 79,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>60,38; 275,61</t>
+          <t>61,69; 280,58</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 50,45</t>
+          <t>-36,11; 48,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,11</t>
+          <t>-0,5; 1,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,69</t>
+          <t>0,8; 2,6</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,51</t>
+          <t>-0,56; 1,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,41</t>
+          <t>-0,68; 1,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,8</t>
+          <t>5,09; 7,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 22,37</t>
+          <t>-0,33; 21,52</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,97</t>
+          <t>-0,32; 0,97</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,94</t>
+          <t>3,36; 4,89</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,78</t>
+          <t>-0,0; 12,06</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 46,48</t>
+          <t>-15,98; 49,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24,92; 113,86</t>
+          <t>22,82; 103,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 63,21</t>
+          <t>-17,99; 53,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 34,39</t>
+          <t>-12,99; 35,32</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>100,0; 189,91</t>
+          <t>100,08; 191,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 516,71</t>
+          <t>-7,25; 471,61</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 27,58</t>
+          <t>-8,14; 28,83</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>79,92; 143,89</t>
+          <t>84,56; 148,08</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 356,2</t>
+          <t>-0,42; 331,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,15</t>
+          <t>-1,56; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,11</t>
+          <t>-0,57; 3,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,72</t>
+          <t>-1,59; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,14</t>
+          <t>-2,38; 1,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,58</t>
+          <t>-0,18; 4,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,92</t>
+          <t>-1,97; 3,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,81</t>
+          <t>-1,5; 0,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,94</t>
+          <t>0,07; 3,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,54</t>
+          <t>-1,43; 2,01</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>-8,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>-3,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-82,7; 172,7</t>
+          <t>-74,66; 237,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 420,49</t>
+          <t>-37,56; 440,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 841,23</t>
+          <t>-100,0; 535,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 95,13</t>
+          <t>-77,84; 103,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 371,1</t>
+          <t>-13,17; 384,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 297,6</t>
+          <t>-73,84; 241,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 68,33</t>
+          <t>-63,94; 65,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 217,69</t>
+          <t>1,76; 257,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,96; 194,22</t>
+          <t>-67,23; 155,0</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,56</t>
+          <t>-2,14; 0,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,8</t>
+          <t>-1,29; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,76</t>
+          <t>-1,41; 3,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,82</t>
+          <t>-0,85; 2,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,15</t>
+          <t>-0,62; 3,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,86</t>
+          <t>-0,49; 4,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,0</t>
+          <t>-1,08; 1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,99</t>
+          <t>-0,51; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,21</t>
+          <t>-0,39; 2,8</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,05; 44,11</t>
+          <t>-72,51; 31,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 136,12</t>
+          <t>-48,3; 132,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 188,13</t>
+          <t>-60,1; 199,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 200,26</t>
+          <t>-34,4; 207,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 234,8</t>
+          <t>-22,7; 247,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 206,24</t>
+          <t>-20,64; 277,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 61,42</t>
+          <t>-39,84; 68,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 126,22</t>
+          <t>-18,77; 118,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 137,92</t>
+          <t>-19,25; 173,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,04</t>
+          <t>-0,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,57</t>
+          <t>-0,97; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,52</t>
+          <t>-1,93; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,55</t>
+          <t>-2,45; 1,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,49</t>
+          <t>-2,42; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,79</t>
+          <t>0,78; 5,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,01</t>
+          <t>-4,03; 0,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,43</t>
+          <t>-1,07; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 3,49</t>
+          <t>0,16; 3,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,38</t>
+          <t>-2,49; 0,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>-8,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,22%</t>
+          <t>-34,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-25,61%</t>
+          <t>-24,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 149,52</t>
+          <t>-24,05; 151,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 114,37</t>
+          <t>-43,3; 107,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,5; 115,12</t>
+          <t>-55,64; 89,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,89; 74,31</t>
+          <t>-42,29; 68,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 166,66</t>
+          <t>9,86; 167,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,1; 2,31</t>
+          <t>-63,48; 9,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 75,37</t>
+          <t>-22,03; 70,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 112,48</t>
+          <t>2,16; 110,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 12,94</t>
+          <t>-50,46; 23,72</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,91</t>
+          <t>-1,02; 3,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,31</t>
+          <t>0,88; 5,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,18</t>
+          <t>0,13; 4,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 2,37</t>
+          <t>-2,96; 2,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 10,18</t>
+          <t>3,47; 10,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,69</t>
+          <t>-2,91; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,91</t>
+          <t>-1,48; 1,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,02</t>
+          <t>2,85; 6,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,86</t>
+          <t>-0,66; 2,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,69%</t>
+          <t>-4,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,18; 226,79</t>
+          <t>-38,97; 228,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,94; 391,24</t>
+          <t>18,37; 374,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,12; 229,68</t>
+          <t>2,64; 330,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,95; 56,15</t>
+          <t>-43,69; 61,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,63; 251,36</t>
+          <t>43,88; 238,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,9; 43,28</t>
+          <t>-37,32; 50,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 62,56</t>
+          <t>-31,16; 64,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>57,02; 226,62</t>
+          <t>57,46; 227,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 58,08</t>
+          <t>-14,83; 85,92</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,79</t>
+          <t>-3,74; 1,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,28</t>
+          <t>-0,3; 6,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,34</t>
+          <t>-2,67; 2,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,24</t>
+          <t>-2,9; 3,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,85; 17,51</t>
+          <t>8,69; 17,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,22</t>
+          <t>-2,25; 3,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,91</t>
+          <t>-2,46; 1,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,69</t>
+          <t>5,62; 11,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,08</t>
+          <t>-1,5; 2,27</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,42%</t>
+          <t>-1,7%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,93; 72,96</t>
+          <t>-61,82; 70,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 237,28</t>
+          <t>-8,69; 257,92</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 85,68</t>
+          <t>-46,46; 85,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 84,73</t>
+          <t>-39,83; 78,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>114,98; 418,33</t>
+          <t>112,74; 424,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 85,97</t>
+          <t>-28,87; 81,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 50,58</t>
+          <t>-40,91; 43,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>91,09; 279,82</t>
+          <t>89,56; 287,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,71; 57,16</t>
+          <t>-24,33; 62,19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,81</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>19,11</t>
+          <t>-0,71</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 3,43</t>
+          <t>-3,03; 3,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,82</t>
+          <t>-3,05; 2,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,8</t>
+          <t>-3,9; 1,9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 6,32</t>
+          <t>-1,92; 6,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,46</t>
+          <t>4,93; 14,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 65,06</t>
+          <t>-4,01; 2,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,9</t>
+          <t>-1,25; 4,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,88</t>
+          <t>1,98; 7,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 53,75</t>
+          <t>-3,0; 1,32</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-20,56%</t>
+          <t>-17,14%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>434,67%</t>
+          <t>-8,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>331,16%</t>
+          <t>-12,33%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 127,04</t>
+          <t>-56,53; 119,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-54,85; 99,6</t>
+          <t>-54,64; 94,13</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 81,75</t>
+          <t>-60,55; 84,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 126,22</t>
+          <t>-22,14; 119,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>51,82; 270,23</t>
+          <t>45,1; 273,44</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 1565,68</t>
+          <t>-41,61; 46,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 82,04</t>
+          <t>-17,86; 89,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28,61; 175,72</t>
+          <t>26,3; 175,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 1249,62</t>
+          <t>-41,99; 30,99</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>-0,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,41</t>
+          <t>-2,39; 5,45</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,49</t>
+          <t>1,23; 8,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,41</t>
+          <t>-1,79; 5,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,16</t>
+          <t>-4,44; 3,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,45</t>
+          <t>5,06; 15,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,95</t>
+          <t>-4,7; 1,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,19</t>
+          <t>-2,48; 2,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,72</t>
+          <t>4,39; 11,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,05</t>
+          <t>-2,62; 2,24</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-17,79%</t>
+          <t>-17,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-3,36%</t>
+          <t>-0,53%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 298,95</t>
+          <t>-52,64; 280,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,11; 484,68</t>
+          <t>15,11; 485,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 251,67</t>
+          <t>-33,54; 282,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 60,09</t>
+          <t>-49,67; 63,78</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>51,45; 313,02</t>
+          <t>50,71; 320,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 43,91</t>
+          <t>-49,34; 42,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-37,03; 79,03</t>
+          <t>-35,25; 72,23</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>61,69; 280,58</t>
+          <t>61,91; 275,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 48,66</t>
+          <t>-35,38; 57,12</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,21</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,14</t>
+          <t>-0,53; 1,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,6</t>
+          <t>0,8; 2,68</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,31</t>
+          <t>-0,14; 1,6</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,44</t>
+          <t>-0,71; 1,4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,78</t>
+          <t>5,19; 7,78</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 21,52</t>
+          <t>-0,79; 1,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,97</t>
+          <t>-0,32; 0,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,89</t>
+          <t>3,38; 5,0</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 12,06</t>
+          <t>-0,13; 1,11</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>113,66%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 49,47</t>
+          <t>-17,06; 48,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>22,82; 103,36</t>
+          <t>23,91; 110,49</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 53,33</t>
+          <t>-4,84; 65,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 35,32</t>
+          <t>-14,37; 33,57</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>100,08; 191,11</t>
+          <t>101,58; 191,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 471,61</t>
+          <t>-14,81; 27,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 28,83</t>
+          <t>-8,16; 29,03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>84,56; 148,08</t>
+          <t>84,69; 146,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 331,04</t>
+          <t>-3,83; 33,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
